--- a/ig/DM-SIDOBA/ValueSet-JDV-J198-FonctionLieu-ROR.xlsx
+++ b/ig/DM-SIDOBA/ValueSet-JDV-J198-FonctionLieu-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260601120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-06-01T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -265,6 +265,12 @@
   </si>
   <si>
     <t>Local de cabinet de ville de pneumologie</t>
+  </si>
+  <si>
+    <t>029</t>
+  </si>
+  <si>
+    <t>Plateau de médecine nucléaire</t>
   </si>
   <si>
     <t/>
@@ -535,7 +541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -779,15 +785,23 @@
         <v>84</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>86</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
